--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 1.691.295,97</t>
-  </si>
-  <si>
-    <t>R$ 9.292,84
-R$ 9.436,34</t>
-  </si>
-  <si>
-    <t>(1.4%)
-0.1%</t>
-  </si>
-  <si>
-    <t>96.9</t>
-  </si>
-  <si>
-    <t>(6.5%)</t>
-  </si>
-  <si>
-    <t>26.2%</t>
-  </si>
-  <si>
-    <t>(18.3%)</t>
+175</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.719.944,24</t>
+  </si>
+  <si>
+    <t>R$ 9.297,00
+R$ 9.438,28</t>
+  </si>
+  <si>
+    <t>(1.3%)
+0.2%</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>(6.2%)</t>
+  </si>
+  <si>
+    <t>29.6%</t>
+  </si>
+  <si>
+    <t>(14.7%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.7</t>
   </si>
   <si>
-    <t>61.3%</t>
-  </si>
-  <si>
-    <t>15.9%</t>
+    <t>61.0%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -962,19 +962,19 @@
     <t>7.7</t>
   </si>
   <si>
-    <t>14.6</t>
+    <t>14.5</t>
   </si>
   <si>
     <t>21.2</t>
   </si>
   <si>
-    <t>62.2%</t>
-  </si>
-  <si>
-    <t>-R$ 51.307,06</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>62.1%</t>
+  </si>
+  <si>
+    <t>-R$ 52.531,59</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>0.20720720720720731</v>
       </c>
       <c r="T7" s="6">
-        <v>0.34242735832877602</v>
+        <v>0.34828049912374387</v>
       </c>
       <c r="U7" s="6">
-        <v>0.010999388350393524</v>
+        <v>0.016852529145361363</v>
       </c>
       <c r="V7" s="6">
         <v>0.026984493836029331</v>
@@ -5841,10 +5841,10 @@
         <v>0.36956521739130443</v>
       </c>
       <c r="T35" s="6">
-        <v>2.4576651058367882</v>
+        <v>10.889540158945255</v>
       </c>
       <c r="U35" s="6">
-        <v>0.20744931775186828</v>
+        <v>8.6393243708603347</v>
       </c>
       <c r="V35" s="6">
         <v>0.053410569814712941</v>
@@ -8720,7 +8720,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8756,25 +8756,59 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>12444.1</v>
+      </c>
+      <c r="P58" s="5">
+        <v>12444.1</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.25737352100152577</v>
+      </c>
+      <c r="R58" s="7">
+        <v>137</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.15126050420168058</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.38546431642304385</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.026556078784323492</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.0099695437998730315</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.001053350583810802</v>
+      </c>
+      <c r="X58" s="8">
+        <v>30.423174285714286</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.31428571428571428</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>6.6127737226277379</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>8.0538095238095231</v>
+      </c>
       <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>22.408254285714285</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.43809523809523809</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-511.5</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -16871,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -23000,7 +23034,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -23036,25 +23070,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>5644.6700000000001</v>
+      </c>
+      <c r="P172" s="5">
+        <v>5644.6700000000001</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>-0.25718252401631791</v>
+      </c>
+      <c r="R172" s="7">
+        <v>63</v>
+      </c>
+      <c r="S172" s="6">
+        <v>-0.086956521739130488</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.26005612374151194</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0036071196367546731</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.052614767559485319</v>
+      </c>
+      <c r="W172" s="6">
+        <v>0.02326495614446903</v>
+      </c>
+      <c r="X172" s="8">
+        <v>19.207232075471698</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>0.96226415094339623</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>4.4048387096774198</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>3.3389943396226416</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>7.7833319999999997</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>14.746226415094339</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.98113207547169812</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>-112.2</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -25931,7 +26001,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25967,25 +26037,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>10559.5</v>
+      </c>
+      <c r="P195" s="5">
+        <v>10559.5</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.19906568374961964</v>
+      </c>
+      <c r="R195" s="7">
+        <v>121</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.17475728155339798</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.31649214451441826</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.003782489701216914</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.013797007434064115</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.001484966144230314</v>
+      </c>
+      <c r="X195" s="8">
+        <v>29.821580769230767</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>5.6540178571428568</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>9.6119653846153845</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.17970128205128</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-600.83000000000004</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-19).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.719.944,24</t>
-  </si>
-  <si>
-    <t>R$ 9.297,00
-R$ 9.438,28</t>
-  </si>
-  <si>
-    <t>(1.3%)
-0.2%</t>
-  </si>
-  <si>
-    <t>97.1</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>29.6%</t>
-  </si>
-  <si>
-    <t>(14.7%)</t>
+176</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.727.479,52</t>
+  </si>
+  <si>
+    <t>R$ 9.287,52
+R$ 9.427,46</t>
+  </si>
+  <si>
+    <t>(1.4%)
+0.1%</t>
+  </si>
+  <si>
+    <t>97.0</t>
+  </si>
+  <si>
+    <t>(6.3%)</t>
+  </si>
+  <si>
+    <t>29.7%</t>
+  </si>
+  <si>
+    <t>(14.6%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.7</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
+    <t>60.8%</t>
+  </si>
+  <si>
+    <t>15.9%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -962,7 +962,7 @@
     <t>7.7</t>
   </si>
   <si>
-    <t>14.5</t>
+    <t>14.6</t>
   </si>
   <si>
     <t>21.2</t>
@@ -971,7 +971,7 @@
     <t>62.1%</t>
   </si>
   <si>
-    <t>-R$ 52.531,59</t>
+    <t>-R$ 52.573,49</t>
   </si>
   <si>
     <t>2.95</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>9.4508956989247324</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>20.203942000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>27.147132258064516</v>
       </c>
@@ -5708,10 +5710,10 @@
         <v>0.0064102564102563875</v>
       </c>
       <c r="T34" s="6">
-        <v>0.29498310995976884</v>
+        <v>0.34512214882135112</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.012726207470929098</v>
+        <v>0.037412831390653212</v>
       </c>
       <c r="V34" s="6">
         <v>0.05726315829262546</v>
@@ -8798,7 +8800,9 @@
       <c r="AB58" s="8">
         <v>8.0538095238095231</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>15.478569999999999</v>
+      </c>
       <c r="AD58" s="8">
         <v>22.408254285714285</v>
       </c>
@@ -10982,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -11016,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>7535.2799999999997</v>
+      </c>
+      <c r="P76" s="5">
+        <v>7535.2799999999997</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.23056940853561403</v>
+      </c>
+      <c r="R76" s="7">
+        <v>87</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.21621621621621623</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.37659737926128828</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.048420669172213902</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.02524544542472211</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.0028560982471786053</v>
+      </c>
+      <c r="X76" s="8">
+        <v>31.547115384615385</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>6.3384123809523816</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>9.3939723404255329</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>16.012542</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>23.591667307692305</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.57692307692307687</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -24025,7 +24065,9 @@
       <c r="AB179" s="8">
         <v>1.9197745762711864</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.1677960000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.120622033898306</v>
       </c>
